--- a/data/trans_dic/P13_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P13_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,35</t>
+          <t>1,33; 5,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,94</t>
+          <t>2,84; 7,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 9,04</t>
+          <t>3,2; 8,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,54</t>
+          <t>0,6; 3,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,55</t>
+          <t>1,46; 6,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,9; 23,75</t>
+          <t>14,03; 24,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 13,86</t>
+          <t>6,66; 14,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,62</t>
+          <t>0,36; 2,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,06</t>
+          <t>1,85; 4,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,23; 14,44</t>
+          <t>9,07; 14,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,78; 10,18</t>
+          <t>5,7; 10,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,55</t>
+          <t>0,66; 2,44</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,99</t>
+          <t>2,92; 7,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,07</t>
+          <t>2,89; 7,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,38</t>
+          <t>1,21; 4,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,59</t>
+          <t>2,55; 6,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 9,11</t>
+          <t>4,56; 8,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,31; 13,99</t>
+          <t>8,39; 14,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,63</t>
+          <t>2,18; 5,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 9,95</t>
+          <t>5,78; 9,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,29</t>
+          <t>4,28; 7,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,58</t>
+          <t>6,3; 9,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,42</t>
+          <t>2,04; 4,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,39</t>
+          <t>4,55; 7,35</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,6</t>
+          <t>0,3; 3,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,49</t>
+          <t>1,22; 5,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,04</t>
+          <t>0,49; 3,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 10,65</t>
+          <t>5,34; 10,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,41</t>
+          <t>0,91; 4,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 9,41</t>
+          <t>4,06; 9,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,35; 13,4</t>
+          <t>8,46; 13,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,26</t>
+          <t>0,79; 3,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,87</t>
+          <t>3,21; 6,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,09</t>
+          <t>0,44; 2,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,44; 11,02</t>
+          <t>7,55; 11,33</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,41</t>
+          <t>0,3; 3,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,51</t>
+          <t>1,38; 4,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,13</t>
+          <t>2,71; 7,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 9,84</t>
+          <t>3,76; 9,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,37</t>
+          <t>1,09; 4,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 12,16</t>
+          <t>6,63; 12,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,9</t>
+          <t>4,56; 10,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,7</t>
+          <t>3,2; 7,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,12</t>
+          <t>1,04; 3,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 7,78</t>
+          <t>4,46; 7,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,88</t>
+          <t>4,29; 7,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,63</t>
+          <t>4,12; 7,78</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,37</t>
+          <t>0,9; 5,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,52</t>
+          <t>1,03; 6,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,85</t>
+          <t>1,84; 6,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,07</t>
+          <t>2,66; 7,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 10,9</t>
+          <t>3,52; 11,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,58; 16,95</t>
+          <t>7,79; 16,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,29; 11,49</t>
+          <t>4,18; 11,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,96</t>
+          <t>3,34; 7,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,89</t>
+          <t>2,93; 6,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 10,05</t>
+          <t>4,99; 10,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 8,0</t>
+          <t>3,7; 8,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,28</t>
+          <t>3,34; 6,29</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,45</t>
+          <t>2,3; 7,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,76</t>
+          <t>2,04; 6,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,98</t>
+          <t>3,48; 7,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,23</t>
+          <t>0,71; 3,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,69; 9,64</t>
+          <t>4,02; 9,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,89; 12,17</t>
+          <t>4,97; 11,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,5</t>
+          <t>6,93; 11,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,03</t>
+          <t>0,36; 2,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,59</t>
+          <t>3,67; 7,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,96; 8,35</t>
+          <t>4,19; 8,74</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,61; 8,84</t>
+          <t>5,63; 8,7</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,64</t>
+          <t>2,93; 6,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,94</t>
+          <t>1,34; 3,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,99</t>
+          <t>2,69; 6,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,0</t>
+          <t>4,88; 8,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,65; 8,67</t>
+          <t>4,72; 8,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,68</t>
+          <t>3,69; 7,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,54; 9,76</t>
+          <t>5,46; 9,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 9,62</t>
+          <t>3,3; 9,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,3; 6,81</t>
+          <t>4,26; 6,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,04</t>
+          <t>2,79; 5,12</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,28</t>
+          <t>4,66; 7,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 8,43</t>
+          <t>4,46; 8,37</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,4</t>
+          <t>3,08; 6,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,02; 11,24</t>
+          <t>6,94; 11,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,24</t>
+          <t>1,78; 4,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,6</t>
+          <t>1,74; 5,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,75</t>
+          <t>4,21; 7,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,3; 12,74</t>
+          <t>8,19; 12,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,33</t>
+          <t>2,35; 5,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,8</t>
+          <t>5,91; 8,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,53</t>
+          <t>4,01; 6,36</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,18; 11,3</t>
+          <t>8,12; 11,21</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,33</t>
+          <t>2,39; 4,25</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,63</t>
+          <t>3,33; 6,69</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,83</t>
+          <t>2,63; 3,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,5</t>
+          <t>3,92; 5,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,13</t>
+          <t>2,84; 4,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,67</t>
+          <t>3,76; 5,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,05; 5,61</t>
+          <t>4,17; 5,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,33; 10,4</t>
+          <t>8,35; 10,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,33</t>
+          <t>4,8; 6,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,68</t>
+          <t>5,57; 7,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,58; 4,56</t>
+          <t>3,57; 4,52</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6,36; 7,68</t>
+          <t>6,42; 7,66</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,05; 5,1</t>
+          <t>4,03; 5,1</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,46</t>
+          <t>5,08; 6,46</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre</t>
+          <t>Población que sus problemas (fìsicos o emocionales) le han dificultado sus actividades sociales siempre o casi siempre (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3356; 14609</t>
+          <t>3620; 15246</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9015; 23406</t>
+          <t>8377; 22425</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9608; 26562</t>
+          <t>9395; 26216</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1551; 11036</t>
+          <t>1882; 11649</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3472; 17096</t>
+          <t>3810; 16208</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39930; 68228</t>
+          <t>40289; 69504</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19856; 40010</t>
+          <t>19221; 40639</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1353; 7578</t>
+          <t>1029; 7146</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9802; 27024</t>
+          <t>9870; 26028</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53738; 84055</t>
+          <t>52807; 85080</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33660; 59316</t>
+          <t>33209; 59988</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4143; 15302</t>
+          <t>3980; 14646</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14315; 34461</t>
+          <t>14388; 34992</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13908; 35684</t>
+          <t>14567; 35438</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6087; 22015</t>
+          <t>6058; 20296</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13738; 34100</t>
+          <t>13173; 34265</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23235; 45896</t>
+          <t>22958; 45047</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43517; 73251</t>
+          <t>43963; 73534</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10565; 29433</t>
+          <t>11410; 29705</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29169; 51251</t>
+          <t>29787; 50228</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43041; 72680</t>
+          <t>42639; 71316</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62455; 98541</t>
+          <t>64822; 100429</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21246; 45292</t>
+          <t>20943; 43019</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47532; 76329</t>
+          <t>46929; 75919</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>956; 11475</t>
+          <t>958; 11030</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4007; 17780</t>
+          <t>3943; 17656</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1639; 9685</t>
+          <t>1574; 10307</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16985; 33560</t>
+          <t>16828; 33697</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3023; 14800</t>
+          <t>3042; 14632</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14338; 32080</t>
+          <t>13852; 32874</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7467</t>
+          <t>0; 7022</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29152; 46795</t>
+          <t>29543; 46991</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5555; 21331</t>
+          <t>5184; 20315</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21401; 45702</t>
+          <t>21317; 43940</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2739; 13701</t>
+          <t>2886; 13201</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>49408; 73206</t>
+          <t>50117; 75231</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1100; 12226</t>
+          <t>1086; 11492</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4368; 16836</t>
+          <t>5149; 17386</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10104; 26314</t>
+          <t>10002; 26315</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11678; 30771</t>
+          <t>11758; 29983</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4739; 16235</t>
+          <t>4062; 16688</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24630; 47069</t>
+          <t>25650; 48257</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17753; 38349</t>
+          <t>17666; 38865</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15344; 36378</t>
+          <t>15095; 36552</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7772; 22785</t>
+          <t>7600; 22892</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33563; 59131</t>
+          <t>33875; 58782</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32575; 59609</t>
+          <t>32463; 58537</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32055; 59893</t>
+          <t>32341; 61047</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1839; 10925</t>
+          <t>1827; 11109</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2389; 13853</t>
+          <t>2197; 12943</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3087; 14477</t>
+          <t>3891; 14163</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4689; 12643</t>
+          <t>4751; 13268</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8050; 22641</t>
+          <t>7308; 22840</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16635; 37215</t>
+          <t>17099; 36408</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9329; 25023</t>
+          <t>9101; 25090</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6744; 14490</t>
+          <t>6945; 14636</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11619; 28307</t>
+          <t>12028; 28226</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22204; 43452</t>
+          <t>21587; 44443</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15618; 34296</t>
+          <t>15870; 35078</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13304; 24303</t>
+          <t>12920; 24337</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1947</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7009; 20399</t>
+          <t>6293; 20962</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5875; 17792</t>
+          <t>5373; 17820</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9969; 21510</t>
+          <t>9376; 20476</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2066; 11760</t>
+          <t>1981; 10905</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10344; 26984</t>
+          <t>11258; 27416</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13343; 33250</t>
+          <t>13585; 32173</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17672; 29564</t>
+          <t>17815; 29866</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1969; 11149</t>
+          <t>1986; 11765</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20246; 42074</t>
+          <t>20351; 41606</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21255; 44800</t>
+          <t>22457; 46884</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29542; 46575</t>
+          <t>29636; 45834</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>18397; 40851</t>
+          <t>18007; 39151</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8018; 26103</t>
+          <t>8889; 25022</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17551; 39344</t>
+          <t>17665; 39389</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30382; 56077</t>
+          <t>30435; 55379</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29700; 55335</t>
+          <t>30142; 56060</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26009; 53216</t>
+          <t>25535; 52528</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38232; 67325</t>
+          <t>37667; 66956</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>28451; 81715</t>
+          <t>28067; 82136</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>53831; 85318</t>
+          <t>53380; 86876</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36946; 68317</t>
+          <t>37825; 69471</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>62128; 98076</t>
+          <t>62756; 97296</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>63993; 124180</t>
+          <t>65634; 123215</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>23632; 47606</t>
+          <t>22939; 45541</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>54604; 87443</t>
+          <t>53993; 88604</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14308; 33013</t>
+          <t>13872; 33792</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14559; 51953</t>
+          <t>16179; 53874</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>33123; 60683</t>
+          <t>32987; 59867</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>68352; 104929</t>
+          <t>67446; 101938</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19311; 43953</t>
+          <t>19373; 43966</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>42506; 63065</t>
+          <t>42368; 64239</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>63460; 99778</t>
+          <t>61268; 97134</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>131093; 180974</t>
+          <t>130126; 179523</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>38282; 69324</t>
+          <t>38305; 68130</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>52636; 109120</t>
+          <t>54716; 110011</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>85961; 125506</t>
+          <t>86111; 127563</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>135106; 188271</t>
+          <t>134333; 185836</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97926; 140090</t>
+          <t>96531; 140779</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>124843; 196052</t>
+          <t>130009; 196862</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>137011; 189635</t>
+          <t>140887; 192328</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>296176; 369679</t>
+          <t>297009; 369396</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>167866; 223954</t>
+          <t>170000; 226190</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>202910; 280723</t>
+          <t>203776; 280250</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>238296; 303755</t>
+          <t>237495; 301003</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>444062; 535778</t>
+          <t>448149; 534402</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>280753; 353544</t>
+          <t>279351; 353703</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>365723; 459618</t>
+          <t>361230; 459412</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P13_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P13_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,58</t>
+          <t>1,23; 5,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 7,61</t>
+          <t>3,19; 8,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 8,92</t>
+          <t>3,24; 8,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,74</t>
+          <t>0,42; 2,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,21</t>
+          <t>1,59; 6,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,03; 24,2</t>
+          <t>13,87; 23,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,66; 14,08</t>
+          <t>6,67; 14,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,47</t>
+          <t>0,43; 2,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,88</t>
+          <t>1,8; 4,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,07; 14,62</t>
+          <t>9,25; 14,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 10,3</t>
+          <t>5,7; 10,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,44</t>
+          <t>0,6; 2,16</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,1</t>
+          <t>2,86; 6,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,02</t>
+          <t>2,65; 6,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,04</t>
+          <t>1,24; 4,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,62</t>
+          <t>2,54; 6,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,94</t>
+          <t>4,68; 8,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,39; 14,04</t>
+          <t>8,13; 14,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,68</t>
+          <t>2,17; 5,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 9,75</t>
+          <t>5,54; 9,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,15</t>
+          <t>4,23; 7,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,77</t>
+          <t>6,14; 9,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,19</t>
+          <t>2,04; 4,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,35</t>
+          <t>4,54; 7,29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,46</t>
+          <t>0,3; 3,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,45</t>
+          <t>1,23; 5,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,24</t>
+          <t>0,52; 3,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 10,7</t>
+          <t>5,15; 10,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,36</t>
+          <t>0,9; 4,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 9,64</t>
+          <t>4,17; 9,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,46; 13,46</t>
+          <t>8,71; 13,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,1</t>
+          <t>0,8; 3,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,61</t>
+          <t>3,07; 6,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,02</t>
+          <t>0,46; 2,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,55; 11,33</t>
+          <t>7,56; 11,08</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,2</t>
+          <t>0,27; 3,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,66</t>
+          <t>1,12; 4,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,13</t>
+          <t>2,66; 7,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 9,59</t>
+          <t>3,44; 9,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,49</t>
+          <t>1,11; 4,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,63; 12,47</t>
+          <t>6,7; 12,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 10,04</t>
+          <t>4,88; 10,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,74</t>
+          <t>5,15; 8,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,14</t>
+          <t>1,07; 3,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,73</t>
+          <t>4,37; 7,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,74</t>
+          <t>4,31; 7,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,78</t>
+          <t>4,84; 8,14</t>
         </is>
       </c>
     </row>
@@ -1224,47 +1224,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>3,93%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,19%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>4,36%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,19%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,46</t>
+          <t>0,89; 5,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,09</t>
+          <t>1,01; 5,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,71</t>
+          <t>1,44; 6,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,42</t>
+          <t>2,22; 6,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 11,0</t>
+          <t>3,74; 11,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 16,58</t>
+          <t>7,54; 16,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 11,52</t>
+          <t>4,24; 11,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 7,03</t>
+          <t>3,13; 6,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,87</t>
+          <t>3,03; 6,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,99; 10,28</t>
+          <t>4,88; 10,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,18</t>
+          <t>3,61; 7,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,29</t>
+          <t>3,16; 5,87</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,65</t>
+          <t>2,31; 7,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,77</t>
+          <t>1,98; 7,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,59</t>
+          <t>3,72; 7,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,92</t>
+          <t>0,71; 4,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,02; 9,79</t>
+          <t>4,01; 9,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,97; 11,78</t>
+          <t>4,77; 12,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 11,62</t>
+          <t>6,77; 11,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,14</t>
+          <t>0,37; 2,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,51</t>
+          <t>3,69; 7,49</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,74</t>
+          <t>4,15; 8,39</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,63; 8,7</t>
+          <t>5,61; 8,55</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,37</t>
+          <t>2,92; 6,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,78</t>
+          <t>1,24; 3,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,0</t>
+          <t>2,7; 6,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,88; 8,89</t>
+          <t>5,22; 9,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,78</t>
+          <t>4,63; 8,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,69; 7,58</t>
+          <t>3,64; 7,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,7</t>
+          <t>5,53; 9,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,3; 9,67</t>
+          <t>7,7; 11,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,26; 6,93</t>
+          <t>4,36; 6,87</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,12</t>
+          <t>2,69; 4,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,23</t>
+          <t>4,57; 7,1</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,37</t>
+          <t>6,93; 9,84</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,12</t>
+          <t>3,11; 6,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,94; 11,39</t>
+          <t>6,91; 11,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,34</t>
+          <t>1,76; 4,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,8</t>
+          <t>3,67; 6,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,64</t>
+          <t>4,36; 7,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,19; 12,37</t>
+          <t>8,06; 12,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,33</t>
+          <t>2,43; 5,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,91; 8,96</t>
+          <t>5,93; 9,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,01; 6,36</t>
+          <t>4,13; 6,39</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8,12; 11,21</t>
+          <t>8,11; 11,2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,25</t>
+          <t>2,37; 4,27</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,69</t>
+          <t>5,21; 7,4</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,63; 3,89</t>
+          <t>2,59; 3,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 5,43</t>
+          <t>3,96; 5,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,15</t>
+          <t>2,85; 4,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,76; 5,7</t>
+          <t>4,55; 6,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,17; 5,69</t>
+          <t>4,15; 5,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,35; 10,39</t>
+          <t>8,41; 10,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,8; 6,39</t>
+          <t>4,77; 6,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,57; 7,66</t>
+          <t>6,79; 8,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,52</t>
+          <t>3,54; 4,54</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6,42; 7,66</t>
+          <t>6,35; 7,7</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,03; 5,1</t>
+          <t>4,05; 5,08</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,46</t>
+          <t>5,9; 6,91</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>7280</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3620; 15246</t>
+          <t>3352; 14941</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8377; 22425</t>
+          <t>9406; 24092</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9395; 26216</t>
+          <t>9512; 25072</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1882; 11649</t>
+          <t>1325; 8870</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3810; 16208</t>
+          <t>4139; 16577</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40289; 69504</t>
+          <t>39849; 66944</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19221; 40639</t>
+          <t>19261; 40689</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1029; 7146</t>
+          <t>1373; 6864</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9870; 26028</t>
+          <t>9634; 25484</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52807; 85080</t>
+          <t>53808; 85813</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33209; 59988</t>
+          <t>33213; 60153</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3980; 14646</t>
+          <t>3813; 13687</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21679</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39190</t>
+          <t>40665</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>60868</t>
+          <t>62903</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14388; 34992</t>
+          <t>14117; 33852</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14567; 35438</t>
+          <t>13357; 35112</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6058; 20296</t>
+          <t>6236; 21640</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13173; 34265</t>
+          <t>13457; 35697</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22958; 45047</t>
+          <t>23562; 45086</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43963; 73534</t>
+          <t>42582; 73579</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11410; 29705</t>
+          <t>11357; 29527</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29787; 50228</t>
+          <t>30265; 51872</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42639; 71316</t>
+          <t>42170; 71721</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64822; 100429</t>
+          <t>63141; 100210</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20943; 43019</t>
+          <t>20925; 43554</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46929; 75919</t>
+          <t>48841; 78489</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23624</t>
+          <t>23149</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37538</t>
+          <t>38670</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61162</t>
+          <t>61819</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>958; 11030</t>
+          <t>952; 10743</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3943; 17656</t>
+          <t>3985; 18216</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1574; 10307</t>
+          <t>1649; 10126</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16828; 33697</t>
+          <t>16229; 31758</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3042; 14632</t>
+          <t>3021; 13846</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13852; 32874</t>
+          <t>14223; 32467</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 7022</t>
+          <t>0; 6756</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29543; 46991</t>
+          <t>31051; 48561</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5184; 20315</t>
+          <t>5264; 19868</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21317; 43940</t>
+          <t>20408; 41896</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2886; 13201</t>
+          <t>3010; 13188</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50117; 75231</t>
+          <t>50769; 74409</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25993</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45646</t>
+          <t>49339</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1086; 11492</t>
+          <t>979; 10782</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5149; 17386</t>
+          <t>4160; 16780</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10002; 26315</t>
+          <t>9815; 26082</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11758; 29983</t>
+          <t>12842; 34580</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4062; 16688</t>
+          <t>4107; 16482</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25650; 48257</t>
+          <t>25942; 48218</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17666; 38865</t>
+          <t>18914; 40305</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15095; 36552</t>
+          <t>21523; 37010</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7600; 22892</t>
+          <t>7798; 22384</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33875; 58782</t>
+          <t>33231; 58766</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32463; 58537</t>
+          <t>32561; 58499</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32341; 61047</t>
+          <t>38297; 64401</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18030</t>
+          <t>18848</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1827; 11109</t>
+          <t>1808; 11085</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2197; 12943</t>
+          <t>2149; 12724</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3891; 14163</t>
+          <t>3044; 14031</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4751; 13268</t>
+          <t>4570; 13103</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7308; 22840</t>
+          <t>7770; 22872</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17099; 36408</t>
+          <t>16561; 35629</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9101; 25090</t>
+          <t>9225; 25723</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6945; 14636</t>
+          <t>7097; 15487</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12028; 28226</t>
+          <t>12441; 28105</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21587; 44443</t>
+          <t>21099; 43438</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15870; 35078</t>
+          <t>15498; 33748</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12920; 24337</t>
+          <t>13668; 25393</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14463</t>
+          <t>14380</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>23102</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>37363</t>
+          <t>37483</t>
         </is>
       </c>
     </row>
@@ -3254,57 +3254,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6293; 20962</t>
+          <t>6322; 20361</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5373; 17820</t>
+          <t>5213; 18411</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9376; 20476</t>
+          <t>10070; 21072</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1981; 10905</t>
+          <t>1979; 12105</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11258; 27416</t>
+          <t>11237; 27086</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13585; 32173</t>
+          <t>13017; 33329</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17815; 29866</t>
+          <t>17864; 29844</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1986; 11765</t>
+          <t>2031; 11725</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20351; 41606</t>
+          <t>20427; 41489</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22457; 46884</t>
+          <t>22251; 44978</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29636; 45834</t>
+          <t>29970; 45683</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41065</t>
+          <t>51349</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>58741</t>
+          <t>72435</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99805</t>
+          <t>123784</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>18007; 39151</t>
+          <t>17945; 38907</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8889; 25022</t>
+          <t>8250; 25412</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17665; 39389</t>
+          <t>17733; 40220</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30435; 55379</t>
+          <t>37490; 69878</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30142; 56060</t>
+          <t>29520; 55143</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25535; 52528</t>
+          <t>25222; 52341</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37667; 66956</t>
+          <t>38183; 68358</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>28067; 82136</t>
+          <t>59426; 87454</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>53380; 86876</t>
+          <t>54601; 86046</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37825; 69471</t>
+          <t>36485; 67495</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>62756; 97296</t>
+          <t>61581; 95574</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>65634; 123215</t>
+          <t>103303; 146670</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35055</t>
+          <t>40251</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>52258</t>
+          <t>60895</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>87313</t>
+          <t>101146</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22939; 45541</t>
+          <t>23167; 45776</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>53993; 88604</t>
+          <t>53730; 88253</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13872; 33792</t>
+          <t>13730; 34635</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16179; 53874</t>
+          <t>29230; 53700</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>32987; 59867</t>
+          <t>34132; 62066</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>67446; 101938</t>
+          <t>66434; 102953</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>19373; 43966</t>
+          <t>20061; 43588</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>42368; 64239</t>
+          <t>49280; 74771</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>61268; 97134</t>
+          <t>63133; 97630</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>130126; 179523</t>
+          <t>129930; 179433</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>38305; 68130</t>
+          <t>38057; 68458</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>54716; 110011</t>
+          <t>84834; 120422</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>168081</t>
+          <t>184452</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>250076</t>
+          <t>278150</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>418157</t>
+          <t>462601</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>86111; 127563</t>
+          <t>84933; 127475</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>134333; 185836</t>
+          <t>135453; 190759</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96531; 140779</t>
+          <t>96776; 141560</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>130009; 196862</t>
+          <t>160618; 213718</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>140887; 192328</t>
+          <t>140324; 190043</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>297009; 369396</t>
+          <t>299047; 365052</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>170000; 226190</t>
+          <t>168680; 224144</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>203776; 280250</t>
+          <t>253214; 305625</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>237495; 301003</t>
+          <t>235509; 302413</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>448149; 534402</t>
+          <t>443214; 537191</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>279351; 353703</t>
+          <t>281018; 352040</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>361230; 459412</t>
+          <t>427953; 501471</t>
         </is>
       </c>
     </row>
